--- a/240308 DoE input file.xlsx
+++ b/240308 DoE input file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cm19ljc\Documents\GitHub\MS-Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA386DB9-B4C5-4955-8637-9325373524C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999EB31F-F702-4103-95FC-CAE93B6F858C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{4E7EF13A-7E46-4B07-B782-DF1F2887ACB6}"/>
+    <workbookView xWindow="34605" yWindow="-6540" windowWidth="14400" windowHeight="7365" activeTab="1" xr2:uid="{4E7EF13A-7E46-4B07-B782-DF1F2887ACB6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -249,9 +249,6 @@
     <t>240214_doe_exp_17_1-1-33_1_9600.d</t>
   </si>
   <si>
-    <t>240214_doe_exp_1_3-2-45_1_9728.d</t>
-  </si>
-  <si>
     <t>240214_doe_exp_2_3-2-46_1_9729.d</t>
   </si>
   <si>
@@ -261,9 +258,6 @@
     <t>240214_doe_exp_4_1-1-26_1_9593.d</t>
   </si>
   <si>
-    <t>240214_doe_exp_5_1-1-27_1_9594.d</t>
-  </si>
-  <si>
     <t>240214_doe_exp_6_1-1-28_1_9595.d</t>
   </si>
   <si>
@@ -277,6 +271,12 @@
   </si>
   <si>
     <t>240308_Nexp_9_3-1-15_1_10664.d</t>
+  </si>
+  <si>
+    <t>240314 Doe_exp_1_2-1-18_1_11646.d</t>
+  </si>
+  <si>
+    <t>240315 Doe_exp_5_2-1-19_1_11647.d</t>
   </si>
 </sst>
 </file>
@@ -759,7 +759,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>502</v>
+        <v>542</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -977,7 +977,7 @@
     </row>
     <row r="2" spans="1:10" ht="14" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="3" spans="1:10" ht="14" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -1041,7 +1041,7 @@
     </row>
     <row r="4" spans="1:10" ht="14" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="6" spans="1:10" ht="14" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -1137,7 +1137,7 @@
     </row>
     <row r="7" spans="1:10" ht="14" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -1169,7 +1169,7 @@
     </row>
     <row r="8" spans="1:10" ht="14" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -1201,7 +1201,7 @@
     </row>
     <row r="9" spans="1:10" ht="14" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -1233,7 +1233,7 @@
     </row>
     <row r="10" spans="1:10" ht="14" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -1265,7 +1265,7 @@
     </row>
     <row r="11" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B11">
         <v>10</v>
